--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B92E63-605C-4F06-BAEB-F7F10A675302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8806A3C-ACB6-4CBE-8473-0C53B4522F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -206,10 +206,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9101,9201,9301,9401,9402,9403,9404,9501,9601,9701,3010000,3010101,3010201,3010301,3010401,3010402,3010403,3010404,3010405,3010501,3010601,3010701,3020000,3020101,3020201,3020301,3020401,3020502,3020603,3020704,3020805,3020501,3020601,3020701,3030000,3030101,3030201,3030301,3030401,3030502,3030603,3030704,3030805,3030501,3030601,3030701,3000101,3000201,3000301,3000401,3000501,3040101,3040102,3040201,3040202,3040301,3040401,3040501,3040601,3040701,3040801,3040901,3041001,3041101,3041102,3041201,3041301,3041401,3041501,3041601,3041701,3041801,3041901,3050000,3050001,3050101,3050102,3050301,3050401,3050501,3050601,3050701,3050801,3050901,3051001,3060000,3060001,3060101,3060102,3060301,3060401,3060501,3060601,3060701,3060801,3060901,3061001,3070000,3070001,3070101,3070102,3070301,3070401,3070501,3070601,3070701,3070801,3070901,3071001,3080000,3080001,3080101,3080102,3080301,3080401,3080501,3080601,3080701,3080801,3080901,3081001,3042001,3042002,3042101,3042102,3042201,3042202,3550100,3550200,3550205,3550206,3550300,3550400,3550500,3550501,3550502,3550503,3550600,3550700,3550701,3550702,3550703,3550800,3550900,3550901,3550902,3551000,3551100,3551101,3551102,3551103,3551200,3551300,3551301,3551302,3551303,3551304,3540100,3540200,3540201,3540205,3540207,3540300,3540400,3540401,3540402,3540405,3540407,3540500,3540600,3540601,3540602,3540605,3540607,3540700,3540800,3540801,3540802,3540805,3540807,3540900,3541000,3541001,3541002,3541005,3541007,3541100,3541200,3541201,3541205,3541207,3541300,3541400,3541401,3541405,3541407,3541500,3541600,3541601,3541602,3541605,3541607,3541700,3541800,3541801,3541802,3541805,3541807,3541900,3542000,3542001,3542002,3542005,3542007,3542100,3542200,3542201,3542202,3542205,3542207,3542300,3542400,3542401,3542405,3542407,3590100,3590200,3590201,3590206,3590300,3590400,3590401,3590402,3590403,3590405,3590407,3590500,3590600,3590601,3590602,3590700,3590800,3590801,3590802,3590805,3590900,3591000,3591001,3591005,3591100,3591200,3591300,3591400,3591401,3591402,3591500,3591600,3591601,3591700,3591800,3591801</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:1_3:2_5:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +219,10 @@
   </si>
   <si>
     <t>42711001:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3010101,3020101,3030101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +660,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -848,7 +848,7 @@
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -873,13 +873,13 @@
         <v>801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8806A3C-ACB6-4CBE-8473-0C53B4522F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEE3FAF-08D0-4FFE-98A9-3E837E4936F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -210,10 +210,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地宫普攻动作档位和普攻目标个数关系（key-个数，value-档次）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>张炽阳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +219,18 @@
   </si>
   <si>
     <t>3010101,3020101,3030101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地宫普攻动作档位和普攻目标个数关系（key-个数，value-档次）（废弃）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地宫普攻动作档位增加普攻目标个数关系（key-档次，value-个数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1_2:2_3:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -567,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -660,7 +668,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -848,7 +856,7 @@
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -873,13 +881,27 @@
         <v>801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>802</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEE3FAF-08D0-4FFE-98A9-3E837E4936F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FF830-EEFE-4B1A-9EFE-05157DB7791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:1_2:2_3:3</t>
+    <t>1:0_2:1_3:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FF830-EEFE-4B1A-9EFE-05157DB7791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEE3FAF-08D0-4FFE-98A9-3E837E4936F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:1_3:3</t>
+    <t>1:1_2:2_3:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FF830-EEFE-4B1A-9EFE-05157DB7791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926C7989-7BE7-4442-A3BD-98D71197695D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:1_3:3</t>
+    <t>1:0_2:2_3:5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926C7989-7BE7-4442-A3BD-98D71197695D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0EFEA4-FF55-4322-80F7-B9FC7DBCA646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:2_3:5</t>
+    <t>1:0_2:3_3:7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0EFEA4-FF55-4322-80F7-B9FC7DBCA646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3447562C-A551-4964-B43F-1EF58E4A4454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:3_3:7</t>
+    <t>1:0_2:2_3:5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3447562C-A551-4964-B43F-1EF58E4A4454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2170EA64-035C-462F-8B22-EA5EB66CCA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:2_3:5</t>
+    <t>1:0_2:2_3:7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2170EA64-035C-462F-8B22-EA5EB66CCA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B0DA57-4280-4D18-8A49-FEB2CDACAFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:2_3:7</t>
+    <t>1:0_2:3_3:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B0DA57-4280-4D18-8A49-FEB2CDACAFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72C0486-BA36-4542-AB49-3759FFEE8782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:0_2:3_3:20</t>
+    <t>1:3_2:3_3:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72C0486-BA36-4542-AB49-3759FFEE8782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A402E8-6967-4EB6-B1A6-0FF9B258D835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -222,15 +222,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地宫普攻动作档位和普攻目标个数关系（key-个数，value-档次）（废弃）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>地宫普攻动作档位增加普攻目标个数关系（key-档次，value-个数）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:3_2:3_3:20</t>
+    <t>1:0_2:0_3:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>地宫普攻动作档位和普攻目标个数关系（key-个数，value-档次）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（废弃）</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -238,7 +250,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,6 +268,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -884,7 +903,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
@@ -898,10 +917,10 @@
         <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A402E8-6967-4EB6-B1A6-0FF9B258D835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886A304B-DC74-4869-A8A8-5A03F9438DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,10 +155,6 @@
   </si>
   <si>
     <t>体力值回复速度 N秒：M点体力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -243,6 +239,22 @@
       </rPr>
       <t>（废弃）</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迷宫体力瓶道具id：对应的体力数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任颖亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>360:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>49000001:60</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -632,7 +644,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -652,7 +664,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -687,7 +699,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -776,151 +788,165 @@
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>301</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>200</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>302</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>200</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>303</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="1"/>
       <c r="E13" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>401</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="1">
-        <v>60</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
+      <c r="A14">
+        <v>304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>501</v>
+        <v>401</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="D15" s="1">
+        <v>60</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
+        <v>501</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>601</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>701</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17">
-        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
+        <v>701</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18">
+        <v>60</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>801</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>802</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886A304B-DC74-4869-A8A8-5A03F9438DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D655C34-8FA1-4FC0-93A8-ABEF32444F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,6 +255,22 @@
   </si>
   <si>
     <t>49000001:60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地宫掉落道具1展示道具id：实际获得道具id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地宫掉落道具2展示道具id：实际获得道具id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200002:46200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700002:46700001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -606,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -949,6 +965,34 @@
         <v>47</v>
       </c>
     </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>901</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>902</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D655C34-8FA1-4FC0-93A8-ABEF32444F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34577CB3-AF3D-470B-8197-F168F9346296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -271,6 +271,14 @@
   </si>
   <si>
     <t>46700002:46700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑战失败补差值，经验系数（万分比）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑战失败补差值，道具装备系数（万分比）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -334,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -342,6 +350,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -622,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -993,6 +1004,42 @@
         <v>56</v>
       </c>
     </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>911</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="7">
+        <v>9500</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>912</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="7">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="7"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34577CB3-AF3D-470B-8197-F168F9346296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E5EDEA-6AF8-4906-AD0E-288F49E9DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,10 +250,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>360:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>49000001:60</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -279,6 +275,10 @@
   </si>
   <si>
     <t>挑战失败补差值，道具装备系数（万分比）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -861,7 +861,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -876,7 +876,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="1"/>
     </row>
@@ -984,10 +984,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -998,10 +998,10 @@
         <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1012,7 +1012,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" s="7">
         <v>9500</v>
@@ -1030,7 +1030,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="7">
         <v>7000</v>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E5EDEA-6AF8-4906-AD0E-288F49E9DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D374BB6D-43DA-4F78-9938-AB6850D1468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1015,7 +1015,7 @@
         <v>56</v>
       </c>
       <c r="D23" s="7">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
@@ -1033,7 +1033,7 @@
         <v>57</v>
       </c>
       <c r="D24" s="7">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D374BB6D-43DA-4F78-9938-AB6850D1468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7E4D28-7FF6-435C-A2D8-584C9C7C846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -262,14 +262,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46200002:46200001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700002:46700001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>挑战失败补差值，经验系数（万分比）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -279,6 +271,14 @@
   </si>
   <si>
     <t>5:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200101:46200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700101:46700001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -861,7 +861,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -987,7 +987,7 @@
         <v>52</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1001,7 +1001,7 @@
         <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1012,7 +1012,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7E4D28-7FF6-435C-A2D8-584C9C7C846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F94009-F1D5-446B-AEFB-D7D7A1B9A130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1015,7 +1015,7 @@
         <v>54</v>
       </c>
       <c r="D23" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F94009-F1D5-446B-AEFB-D7D7A1B9A130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D22122-053C-4E5D-8512-5D29530A59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -279,6 +279,14 @@
   </si>
   <si>
     <t>46700101:46700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宋振扬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关值初始值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -633,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1040,6 +1048,20 @@
       </c>
       <c r="F24" s="7"/>
     </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>921</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="7">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D22122-053C-4E5D-8512-5D29530A59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DBCBFB-1A4F-4985-9910-7DEB843D4241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,6 +287,18 @@
   </si>
   <si>
     <t>通关值初始值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>于翔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同类型敌人增加的砝码值进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1_4:50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -641,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1062,6 +1074,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>931</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DBCBFB-1A4F-4985-9910-7DEB843D4241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D22122-053C-4E5D-8512-5D29530A59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,18 +287,6 @@
   </si>
   <si>
     <t>通关值初始值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>于翔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不同类型敌人增加的砝码值进度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1_4:50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -653,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1074,20 +1062,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>931</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DBCBFB-1A4F-4985-9910-7DEB843D4241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849B13BF-337B-4B34-B297-B4A32DEBC698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -299,6 +299,14 @@
   </si>
   <si>
     <t>1:1_4:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可选择词条组数量上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不限制词条组数量的特殊词条组id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -653,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1088,6 +1096,34 @@
         <v>63</v>
       </c>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>941</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>942</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="7">
+        <v>6009</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849B13BF-337B-4B34-B297-B4A32DEBC698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36AF33F-53DB-408E-9D6D-63E71DECD6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="68">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -307,6 +307,14 @@
   </si>
   <si>
     <t>不限制词条组数量的特殊词条组id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战区同时拥有血瓶上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曹峻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -661,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1124,6 +1132,20 @@
         <v>6009</v>
       </c>
     </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>951</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="7">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_config_v8【迷宫-通用配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36AF33F-53DB-408E-9D6D-63E71DECD6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0FDA3A-8018-434C-90CE-6F8A34D61357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_config_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -310,11 +310,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>战区同时拥有血瓶上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>曹峻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产艳兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血瓶使用CD属性id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战区同时拥有血瓶上限属性id：血瓶id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>890024:48300001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -669,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1137,13 +1149,28 @@
         <v>951</v>
       </c>
       <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>952</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="7">
-        <v>4</v>
+      <c r="C30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="7">
+        <v>890023</v>
       </c>
     </row>
   </sheetData>
